--- a/data/trans_orig/IP2905_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>39662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>39840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>64171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175709</t>
+          <t>175800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213111</t>
+          <t>211395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221178</t>
+          <t>221620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271357</t>
+          <t>271558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>408130</t>
+          <t>405928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>469984</t>
+          <t>468201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206807</t>
+          <t>208523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244209</t>
+          <t>244118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230714</t>
+          <t>230513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280893</t>
+          <t>280451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452005</t>
+          <t>453788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>513859</t>
+          <t>516061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71644</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90834</t>
+          <t>90664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94514</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117924</t>
+          <t>118296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172851</t>
+          <t>170887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204500</t>
+          <t>202862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52698</t>
+          <t>52868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>71983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84115</t>
+          <t>84214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117660</t>
+          <t>119298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149309</t>
+          <t>151273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284215</t>
+          <t>285420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>328451</t>
+          <t>329485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>347770</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>404953</t>
+          <t>404445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647670</t>
+          <t>649453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>718829</t>
+          <t>719706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288697</t>
+          <t>287663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332933</t>
+          <t>331728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334091</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391274</t>
+          <t>390183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>637363</t>
+          <t>636486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708522</t>
+          <t>706739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2905_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22233</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15941</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28884</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32295</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24240</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39662</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>49202</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47872</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69866</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24831</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37774</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>58,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21404</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14037</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29459</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>50418</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42177</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64171</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>224132</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>203706</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>246423</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>193509</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>175800</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>211395</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>244096</t>
+          <t>189734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221620</t>
+          <t>173977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271558</t>
+          <t>207000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>437605</t>
+          <t>413867</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>405928</t>
+          <t>386336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>468201</t>
+          <t>444295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>239228</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>216937</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>259654</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>226409</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>208523</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>244118</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>257975</t>
+          <t>226274</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>209008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280451</t>
+          <t>242031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>484384</t>
+          <t>465501</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>453788</t>
+          <t>435073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>516061</t>
+          <t>493032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463360</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>502071</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>921989</t>
+          <t>879368</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>921989</t>
+          <t>879368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>921989</t>
+          <t>879368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96729</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86364</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>107924</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>81269</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71549</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>90664</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106585</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94415</t>
+          <t>72706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118296</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>179176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170887</t>
+          <t>163092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202862</t>
+          <t>193371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67537</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56342</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77902</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>62263</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71983</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84214</t>
+          <t>71662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>134307</t>
+          <t>129457</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119298</t>
+          <t>115262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151273</t>
+          <t>145541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>143532</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>143532</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>143532</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>322160</t>
+          <t>308633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>322160</t>
+          <t>308633</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>322160</t>
+          <t>308633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>343094</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>318777</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>369021</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>307072</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>285420</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>329485</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>49,76%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>348861</t>
+          <t>279774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>404445</t>
+          <t>321101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>649453</t>
+          <t>610910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>719706</t>
+          <t>673305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>310076</t>
+          <t>338247</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287663</t>
+          <t>312320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331728</t>
+          <t>362564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>307129</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>285179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>390183</t>
+          <t>326506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>673038</t>
+          <t>645376</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636486</t>
+          <t>614316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706739</t>
+          <t>676711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>905</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>617148</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>617148</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>617148</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606280</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1356192</t>
+          <t>1287621</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1356192</t>
+          <t>1287621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1356192</t>
+          <t>1287621</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
